--- a/InputData/elec/ETCMbTCT/Elec Tech Cost Multiplier by Tech Cost Tier.xlsx
+++ b/InputData/elec/ETCMbTCT/Elec Tech Cost Multiplier by Tech Cost Tier.xlsx
@@ -1,38 +1,51 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\IA\elec\ETCMbTCT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\elec\ETCMbTCT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46F01841-C65F-4C8B-ABD4-ED78F9150066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FBC994C-D377-4CD1-B01D-77CDC60592A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="3900" windowWidth="21600" windowHeight="12645" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4125" yWindow="1350" windowWidth="23010" windowHeight="13800" activeTab="1" xr2:uid="{5E78EF81-321F-43F5-B343-4E83A6575A8A}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="ETCMbTCT" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+  <si>
+    <t>Source:</t>
+  </si>
+  <si>
+    <t>none needed, this is a calibrated variable</t>
+  </si>
   <si>
     <t>ETCMbTCT Electricity Technology Cost Multiplier by Technology Cost Tier</t>
-  </si>
-  <si>
-    <t>Iowa</t>
-  </si>
-  <si>
-    <t>Source:</t>
-  </si>
-  <si>
-    <t>none needed, this is a calibrated variable</t>
   </si>
   <si>
     <t>Unit: dimensionless (% of cost costs)</t>
@@ -419,24 +432,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31DA106A-E484-4E2B-B3F9-91B326CF3E2A}">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -445,7 +455,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ABB53E3-B52E-4F21-A58E-08755890D033}">
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
@@ -457,12 +467,12 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -470,7 +480,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>1.33</v>
@@ -478,7 +488,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4">
         <v>1.66</v>
@@ -486,7 +496,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -494,7 +504,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6">
         <v>2.33</v>
